--- a/results/qc/glass_expression_QC.xlsx
+++ b/results/qc/glass_expression_QC.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,44 +417,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n_missing</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_negative</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>n_0</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>n_expressed</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>mean_TPM</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>median_TPM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>max_TPM</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>GLSS-SM-R109-TP</t>
         </is>
@@ -494,7 +482,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>GLSS-19-0274-TP</t>
         </is>
@@ -522,7 +510,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>GLSS-CU-R005-TP</t>
         </is>
@@ -550,7 +538,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>GLSS-SM-R060-TP</t>
         </is>
@@ -578,7 +566,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>GLSS-LU-00C2-TP</t>
         </is>
@@ -606,7 +594,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>GLSS-LU-00B9-R1</t>
         </is>
@@ -634,7 +622,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>TCGA-06-0210-TP</t>
         </is>
@@ -662,7 +650,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>GLSS-SN-0001-R1</t>
         </is>
@@ -690,7 +678,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>GLSS-MD-0022-TP</t>
         </is>
@@ -718,7 +706,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>GLSS-19-0267-R1</t>
         </is>
@@ -746,7 +734,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>GLSS-HF-DF35-TP</t>
         </is>
@@ -774,7 +762,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>GLSS-HF-6504-TP</t>
         </is>
@@ -802,7 +790,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>GLSS-SM-R107-TP</t>
         </is>
@@ -830,7 +818,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>GLSS-SM-R070-TP</t>
         </is>
@@ -858,7 +846,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>GLSS-SM-R101-R1</t>
         </is>
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>GLSS-CU-P069-TP</t>
         </is>
@@ -914,7 +902,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>TCGA-19-0957-R1</t>
         </is>
@@ -942,7 +930,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>GLSS-SN-0009-TP</t>
         </is>
@@ -970,7 +958,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>GLSS-19-0271-R1</t>
         </is>
@@ -998,7 +986,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>GLSS-19-0280-R1</t>
         </is>
@@ -1026,7 +1014,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>GLSS-LX-0304-R1</t>
         </is>
@@ -1054,7 +1042,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>GLSS-SM-R083-TP</t>
         </is>
@@ -1082,7 +1070,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>GLSS-SM-R064-TP</t>
         </is>
@@ -1110,7 +1098,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>GLSS-SN-0002-TP</t>
         </is>
@@ -1138,7 +1126,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>GLSS-SM-R080-TP</t>
         </is>
@@ -1166,7 +1154,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>GLSS-SM-R091-TP</t>
         </is>
@@ -1194,7 +1182,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>GLSS-SM-R106-TP</t>
         </is>
@@ -1222,7 +1210,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>GLSS-SN-0010-TP</t>
         </is>
@@ -1250,7 +1238,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>GLSS-CU-R002-TP</t>
         </is>
@@ -1278,7 +1266,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>GLSS-SM-R091-R1</t>
         </is>
@@ -1306,7 +1294,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>GLSS-CU-P102-R1</t>
         </is>
@@ -1334,7 +1322,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>TCGA-19-4065-TP</t>
         </is>
@@ -1362,7 +1350,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>GLSS-SM-R082-R1</t>
         </is>
@@ -1390,7 +1378,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>GLSS-19-0272-R1</t>
         </is>
@@ -1418,7 +1406,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>GLSS-MD-0035-R1</t>
         </is>
@@ -1446,7 +1434,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>GLSS-HF-9A7A-TP</t>
         </is>
@@ -1474,7 +1462,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>GLSS-HF-2919-R1</t>
         </is>
@@ -1502,7 +1490,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>GLSS-LU-0B10-TP</t>
         </is>
@@ -1530,7 +1518,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>GLSS-SM-R093-R1</t>
         </is>
@@ -1558,7 +1546,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>TCGA-06-0190-TP</t>
         </is>
@@ -1586,7 +1574,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>TCGA-06-0125-TP</t>
         </is>
@@ -1614,7 +1602,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>GLSS-HK-0001-TP</t>
         </is>
@@ -1642,7 +1630,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>GLSS-HF-DF35-R1</t>
         </is>
@@ -1670,7 +1658,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>GLSS-SM-R087-TP</t>
         </is>
@@ -1698,7 +1686,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>GLSS-MD-0026-TP</t>
         </is>
@@ -1726,7 +1714,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>GLSS-SM-R066-TP</t>
         </is>
@@ -1754,7 +1742,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>TCGA-06-0211-R1</t>
         </is>
@@ -1782,7 +1770,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>GLSS-SN-0006-TP</t>
         </is>
@@ -1810,7 +1798,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>GLSS-HF-6504-R1</t>
         </is>
@@ -1838,7 +1826,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>GLSS-CU-P003-R1</t>
         </is>
@@ -1866,7 +1854,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>GLSS-SM-R067-TP</t>
         </is>
@@ -1894,7 +1882,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>GLSS-HF-4D9A-TP</t>
         </is>
@@ -1922,7 +1910,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>GLSS-SM-R081-TP</t>
         </is>
@@ -1950,7 +1938,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>GLSS-CU-R001-R1</t>
         </is>
@@ -1978,7 +1966,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>GLSS-LU-00B9-TP</t>
         </is>
@@ -2006,7 +1994,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>GLSS-SM-R061-TP</t>
         </is>
@@ -2034,7 +2022,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>GLSS-LU-0B13-R1</t>
         </is>
@@ -2062,7 +2050,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>GLSS-SM-R101-TP</t>
         </is>
@@ -2090,7 +2078,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>GLSS-HF-9A7A-R1</t>
         </is>
@@ -2118,7 +2106,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>GLSS-SM-R095-TP</t>
         </is>
@@ -2146,7 +2134,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>GLSS-CU-P069-R1</t>
         </is>
@@ -2174,7 +2162,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>GLSS-HF-2934-TP</t>
         </is>
@@ -2202,7 +2190,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>GLSS-SM-R107-R1</t>
         </is>
@@ -2230,7 +2218,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>GLSS-HK-0003-R1</t>
         </is>
@@ -2258,7 +2246,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>GLSS-SM-R108-R1</t>
         </is>
@@ -2286,7 +2274,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>GLSS-19-0272-TP</t>
         </is>
@@ -2314,7 +2302,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>GLSS-CU-P055-TP</t>
         </is>
@@ -2342,7 +2330,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>GLSS-HF-6658-R1</t>
         </is>
@@ -2370,7 +2358,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>GLSS-SM-R110-R1</t>
         </is>
@@ -2398,7 +2386,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>GLSS-SM-R100-TP</t>
         </is>
@@ -2426,7 +2414,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>GLSS-CU-R007-R1</t>
         </is>
@@ -2454,7 +2442,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>GLSS-19-0278-TP</t>
         </is>
@@ -2482,7 +2470,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>GLSS-HF-DE05-R1</t>
         </is>
@@ -2510,7 +2498,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>GLSS-SM-R083-R1</t>
         </is>
@@ -2538,7 +2526,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>GLSS-SM-R068-R1</t>
         </is>
@@ -2566,7 +2554,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>GLSS-SM-R065-TP</t>
         </is>
@@ -2594,7 +2582,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>GLSS-CU-P055-R1</t>
         </is>
@@ -2622,7 +2610,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>TCGA-06-0210-R1</t>
         </is>
@@ -2650,7 +2638,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>GLSS-SM-R112-TP</t>
         </is>
@@ -2678,7 +2666,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>GLSS-CU-R004-R1</t>
         </is>
@@ -2706,7 +2694,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>GLSS-SM-R082-TP</t>
         </is>
@@ -2734,7 +2722,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>GLSS-SN-0009-R1</t>
         </is>
@@ -2762,7 +2750,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>GLSS-HF-57AE-TP</t>
         </is>
@@ -2790,7 +2778,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>GLSS-LU-00C2-R1</t>
         </is>
@@ -2818,7 +2806,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>GLSS-19-0280-TP</t>
         </is>
@@ -2846,7 +2834,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>GLSS-MD-0042-R1</t>
         </is>
@@ -2874,7 +2862,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>GLSS-CU-R003-R1</t>
         </is>
@@ -2902,7 +2890,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>GLSS-HF-B972-TP</t>
         </is>
@@ -2930,7 +2918,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>GLSS-CU-R003-TP</t>
         </is>
@@ -2958,7 +2946,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>GLSS-MD-LP04-R1</t>
         </is>
@@ -2986,7 +2974,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>TCGA-06-0211-TP</t>
         </is>
@@ -3014,7 +3002,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>GLSS-MD-0035-TP</t>
         </is>
@@ -3042,7 +3030,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>GLSS-HF-2548-TP</t>
         </is>
@@ -3070,7 +3058,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>GLSS-LX-0561-R1</t>
         </is>
@@ -3098,7 +3086,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>GLSS-19-0273-R1</t>
         </is>
@@ -3126,7 +3114,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>GLSS-HF-B972-R1</t>
         </is>
@@ -3154,7 +3142,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>GLSS-SN-0004-TP</t>
         </is>
@@ -3182,7 +3170,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>TCGA-14-1034-R1</t>
         </is>
@@ -3210,7 +3198,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>GLSS-SM-R060-R1</t>
         </is>
@@ -3238,7 +3226,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>GLSS-HF-4D9A-R1</t>
         </is>
@@ -3266,7 +3254,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="inlineStr">
+      <c r="A102" t="inlineStr">
         <is>
           <t>GLSS-SM-R071-TP</t>
         </is>
@@ -3294,7 +3282,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="inlineStr">
+      <c r="A103" t="inlineStr">
         <is>
           <t>GLSS-CU-R006-R1</t>
         </is>
@@ -3322,7 +3310,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="inlineStr">
+      <c r="A104" t="inlineStr">
         <is>
           <t>GLSS-19-0274-R1</t>
         </is>
@@ -3350,7 +3338,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="inlineStr">
+      <c r="A105" t="inlineStr">
         <is>
           <t>GLSS-SM-R071-R1</t>
         </is>
@@ -3378,7 +3366,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="inlineStr">
+      <c r="A106" t="inlineStr">
         <is>
           <t>GLSS-SM-R081-R1</t>
         </is>
@@ -3406,7 +3394,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="inlineStr">
+      <c r="A107" t="inlineStr">
         <is>
           <t>GLSS-HF-2548-R1</t>
         </is>
@@ -3434,7 +3422,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="inlineStr">
+      <c r="A108" t="inlineStr">
         <is>
           <t>GLSS-SN-0016-TP</t>
         </is>
@@ -3462,7 +3450,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="inlineStr">
+      <c r="A109" t="inlineStr">
         <is>
           <t>GLSS-SM-R111-R1</t>
         </is>
@@ -3490,7 +3478,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="inlineStr">
+      <c r="A110" t="inlineStr">
         <is>
           <t>GLSS-19-0267-TP</t>
         </is>
@@ -3518,7 +3506,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="inlineStr">
+      <c r="A111" t="inlineStr">
         <is>
           <t>GLSS-SN-0002-R1</t>
         </is>
@@ -3546,7 +3534,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="inlineStr">
+      <c r="A112" t="inlineStr">
         <is>
           <t>GLSS-19-0268-TP</t>
         </is>
@@ -3574,7 +3562,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="inlineStr">
+      <c r="A113" t="inlineStr">
         <is>
           <t>GLSS-SM-R066-R1</t>
         </is>
@@ -3602,7 +3590,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="inlineStr">
+      <c r="A114" t="inlineStr">
         <is>
           <t>GLSS-SM-R109-R1</t>
         </is>
@@ -3630,7 +3618,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="inlineStr">
+      <c r="A115" t="inlineStr">
         <is>
           <t>GLSS-LU-00C1-R1</t>
         </is>
@@ -3658,7 +3646,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="inlineStr">
+      <c r="A116" t="inlineStr">
         <is>
           <t>GLSS-MD-LP04-TP</t>
         </is>
@@ -3686,7 +3674,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="inlineStr">
+      <c r="A117" t="inlineStr">
         <is>
           <t>GLSS-HF-2919-TP</t>
         </is>
@@ -3714,7 +3702,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="inlineStr">
+      <c r="A118" t="inlineStr">
         <is>
           <t>GLSS-CU-R019-R1</t>
         </is>
@@ -3742,7 +3730,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="inlineStr">
+      <c r="A119" t="inlineStr">
         <is>
           <t>GLSS-HF-1DDC-R1</t>
         </is>
@@ -3770,7 +3758,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="inlineStr">
+      <c r="A120" t="inlineStr">
         <is>
           <t>GLSS-HF-6658-TP</t>
         </is>
@@ -3798,7 +3786,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="inlineStr">
+      <c r="A121" t="inlineStr">
         <is>
           <t>GLSS-19-0268-R1</t>
         </is>
@@ -3826,7 +3814,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="inlineStr">
+      <c r="A122" t="inlineStr">
         <is>
           <t>GLSS-SM-R099-R1</t>
         </is>
@@ -3854,7 +3842,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="inlineStr">
+      <c r="A123" t="inlineStr">
         <is>
           <t>GLSS-CU-R006-TP</t>
         </is>
@@ -3882,7 +3870,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="inlineStr">
+      <c r="A124" t="inlineStr">
         <is>
           <t>GLSS-19-0269-R1</t>
         </is>
@@ -3910,7 +3898,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="inlineStr">
+      <c r="A125" t="inlineStr">
         <is>
           <t>GLSS-SM-R104-TP</t>
         </is>
@@ -3938,7 +3926,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="inlineStr">
+      <c r="A126" t="inlineStr">
         <is>
           <t>GLSS-19-0269-TP</t>
         </is>
@@ -3966,7 +3954,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="inlineStr">
+      <c r="A127" t="inlineStr">
         <is>
           <t>GLSS-HF-EE74-TP</t>
         </is>
@@ -3994,7 +3982,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="inlineStr">
+      <c r="A128" t="inlineStr">
         <is>
           <t>GLSS-HF-3050-TP</t>
         </is>
@@ -4022,7 +4010,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="inlineStr">
+      <c r="A129" t="inlineStr">
         <is>
           <t>GLSS-SM-R064-R1</t>
         </is>
@@ -4050,7 +4038,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="inlineStr">
+      <c r="A130" t="inlineStr">
         <is>
           <t>GLSS-MD-0042-TP</t>
         </is>
@@ -4078,7 +4066,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="inlineStr">
+      <c r="A131" t="inlineStr">
         <is>
           <t>GLSS-HF-1DDC-TP</t>
         </is>
@@ -4106,7 +4094,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="inlineStr">
+      <c r="A132" t="inlineStr">
         <is>
           <t>GLSS-CU-R008-TP</t>
         </is>
@@ -4134,7 +4122,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="inlineStr">
+      <c r="A133" t="inlineStr">
         <is>
           <t>GLSS-SM-R103-TP</t>
         </is>
@@ -4162,7 +4150,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="inlineStr">
+      <c r="A134" t="inlineStr">
         <is>
           <t>GLSS-LX-0561-TP</t>
         </is>
@@ -4190,7 +4178,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="inlineStr">
+      <c r="A135" t="inlineStr">
         <is>
           <t>GLSS-HF-DE05-TP</t>
         </is>
@@ -4218,7 +4206,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="inlineStr">
+      <c r="A136" t="inlineStr">
         <is>
           <t>TCGA-06-0190-R1</t>
         </is>
@@ -4246,7 +4234,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="inlineStr">
+      <c r="A137" t="inlineStr">
         <is>
           <t>GLSS-SM-R085-R1</t>
         </is>
@@ -4274,7 +4262,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="inlineStr">
+      <c r="A138" t="inlineStr">
         <is>
           <t>GLSS-LU-0B10-R1</t>
         </is>
@@ -4302,7 +4290,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="inlineStr">
+      <c r="A139" t="inlineStr">
         <is>
           <t>GLSS-SN-0006-R1</t>
         </is>
@@ -4330,7 +4318,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="inlineStr">
+      <c r="A140" t="inlineStr">
         <is>
           <t>GLSS-MD-0022-R1</t>
         </is>
@@ -4358,7 +4346,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="inlineStr">
+      <c r="A141" t="inlineStr">
         <is>
           <t>GLSS-SM-R087-R1</t>
         </is>
@@ -4386,7 +4374,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="inlineStr">
+      <c r="A142" t="inlineStr">
         <is>
           <t>GLSS-SM-R112-R1</t>
         </is>
@@ -4414,7 +4402,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="inlineStr">
+      <c r="A143" t="inlineStr">
         <is>
           <t>GLSS-HF-3162-TP</t>
         </is>
@@ -4442,7 +4430,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="inlineStr">
+      <c r="A144" t="inlineStr">
         <is>
           <t>GLSS-SM-R072-TP</t>
         </is>
@@ -4470,7 +4458,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="inlineStr">
+      <c r="A145" t="inlineStr">
         <is>
           <t>GLSS-SM-R108-TP</t>
         </is>
@@ -4498,7 +4486,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="inlineStr">
+      <c r="A146" t="inlineStr">
         <is>
           <t>TCGA-19-0957-TP</t>
         </is>
@@ -4526,7 +4514,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="inlineStr">
+      <c r="A147" t="inlineStr">
         <is>
           <t>GLSS-SM-R099-TP</t>
         </is>
@@ -4554,7 +4542,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="inlineStr">
+      <c r="A148" t="inlineStr">
         <is>
           <t>GLSS-CU-R010-TP</t>
         </is>
@@ -4582,7 +4570,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="inlineStr">
+      <c r="A149" t="inlineStr">
         <is>
           <t>GLSS-SN-0001-TP</t>
         </is>
@@ -4610,7 +4598,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="inlineStr">
+      <c r="A150" t="inlineStr">
         <is>
           <t>GLSS-19-0278-R1</t>
         </is>
@@ -4638,7 +4626,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="inlineStr">
+      <c r="A151" t="inlineStr">
         <is>
           <t>GLSS-CU-R005-R1</t>
         </is>
@@ -4666,7 +4654,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="inlineStr">
+      <c r="A152" t="inlineStr">
         <is>
           <t>GLSS-SN-0003-TP</t>
         </is>
@@ -4694,7 +4682,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="inlineStr">
+      <c r="A153" t="inlineStr">
         <is>
           <t>GLSS-SM-R063-TP</t>
         </is>
@@ -4722,7 +4710,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="inlineStr">
+      <c r="A154" t="inlineStr">
         <is>
           <t>GLSS-CU-R004-TP</t>
         </is>
@@ -4750,7 +4738,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="inlineStr">
+      <c r="A155" t="inlineStr">
         <is>
           <t>TCGA-19-4065-R1</t>
         </is>
@@ -4778,7 +4766,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="inlineStr">
+      <c r="A156" t="inlineStr">
         <is>
           <t>GLSS-SM-R093-TP</t>
         </is>
@@ -4806,7 +4794,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="inlineStr">
+      <c r="A157" t="inlineStr">
         <is>
           <t>GLSS-SM-R110-TP</t>
         </is>
@@ -4834,7 +4822,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="inlineStr">
+      <c r="A158" t="inlineStr">
         <is>
           <t>GLSS-SN-0003-R1</t>
         </is>
@@ -4862,7 +4850,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="inlineStr">
+      <c r="A159" t="inlineStr">
         <is>
           <t>GLSS-CU-P046-TP</t>
         </is>
@@ -4890,7 +4878,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="inlineStr">
+      <c r="A160" t="inlineStr">
         <is>
           <t>GLSS-LU-0B13-TP</t>
         </is>
@@ -4918,7 +4906,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="inlineStr">
+      <c r="A161" t="inlineStr">
         <is>
           <t>GLSS-SM-R088-TP</t>
         </is>
@@ -4946,7 +4934,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="inlineStr">
+      <c r="A162" t="inlineStr">
         <is>
           <t>GLSS-CU-R001-TP</t>
         </is>
@@ -4974,7 +4962,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="inlineStr">
+      <c r="A163" t="inlineStr">
         <is>
           <t>GLSS-CU-R019-TP</t>
         </is>
@@ -5002,7 +4990,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="inlineStr">
+      <c r="A164" t="inlineStr">
         <is>
           <t>GLSS-HF-3162-R1</t>
         </is>
@@ -5030,7 +5018,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="inlineStr">
+      <c r="A165" t="inlineStr">
         <is>
           <t>GLSS-19-0271-TP</t>
         </is>
@@ -5058,7 +5046,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="inlineStr">
+      <c r="A166" t="inlineStr">
         <is>
           <t>GLSS-SM-R085-TP</t>
         </is>
@@ -5086,7 +5074,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="inlineStr">
+      <c r="A167" t="inlineStr">
         <is>
           <t>GLSS-CU-R010-R1</t>
         </is>
@@ -5114,7 +5102,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="inlineStr">
+      <c r="A168" t="inlineStr">
         <is>
           <t>GLSS-CU-P102-TP</t>
         </is>
@@ -5142,7 +5130,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="inlineStr">
+      <c r="A169" t="inlineStr">
         <is>
           <t>GLSS-CU-R008-R1</t>
         </is>
@@ -5170,7 +5158,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="inlineStr">
+      <c r="A170" t="inlineStr">
         <is>
           <t>GLSS-SM-R088-R1</t>
         </is>
@@ -5198,7 +5186,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="inlineStr">
+      <c r="A171" t="inlineStr">
         <is>
           <t>TCGA-06-0125-R1</t>
         </is>
@@ -5226,7 +5214,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="inlineStr">
+      <c r="A172" t="inlineStr">
         <is>
           <t>GLSS-HK-0001-R1</t>
         </is>
@@ -5254,7 +5242,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="inlineStr">
+      <c r="A173" t="inlineStr">
         <is>
           <t>GLSS-CU-R007-TP</t>
         </is>
@@ -5282,7 +5270,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="inlineStr">
+      <c r="A174" t="inlineStr">
         <is>
           <t>GLSS-SM-R070-R1</t>
         </is>
@@ -5310,7 +5298,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="inlineStr">
+      <c r="A175" t="inlineStr">
         <is>
           <t>GLSS-LU-0B12-R1</t>
         </is>
@@ -5338,7 +5326,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="inlineStr">
+      <c r="A176" t="inlineStr">
         <is>
           <t>TCGA-14-1034-TP</t>
         </is>
@@ -5366,7 +5354,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="inlineStr">
+      <c r="A177" t="inlineStr">
         <is>
           <t>GLSS-CU-P003-TP</t>
         </is>
@@ -5394,7 +5382,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="inlineStr">
+      <c r="A178" t="inlineStr">
         <is>
           <t>GLSS-CU-P046-R1</t>
         </is>
@@ -5422,7 +5410,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="inlineStr">
+      <c r="A179" t="inlineStr">
         <is>
           <t>GLSS-LU-00C1-TP</t>
         </is>
@@ -5450,7 +5438,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="inlineStr">
+      <c r="A180" t="inlineStr">
         <is>
           <t>GLSS-SM-R111-TP</t>
         </is>
@@ -5478,7 +5466,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="inlineStr">
+      <c r="A181" t="inlineStr">
         <is>
           <t>GLSS-SM-R067-R1</t>
         </is>
@@ -5506,7 +5494,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="inlineStr">
+      <c r="A182" t="inlineStr">
         <is>
           <t>GLSS-SM-R100-R1</t>
         </is>
@@ -5534,7 +5522,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="inlineStr">
+      <c r="A183" t="inlineStr">
         <is>
           <t>GLSS-MD-0026-R1</t>
         </is>
@@ -5562,7 +5550,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="inlineStr">
+      <c r="A184" t="inlineStr">
         <is>
           <t>GLSS-HF-EE74-R1</t>
         </is>
@@ -5590,7 +5578,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="inlineStr">
+      <c r="A185" t="inlineStr">
         <is>
           <t>GLSS-CU-R002-R1</t>
         </is>
@@ -5618,7 +5606,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="inlineStr">
+      <c r="A186" t="inlineStr">
         <is>
           <t>GLSS-HK-0003-TP</t>
         </is>
@@ -5646,7 +5634,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="inlineStr">
+      <c r="A187" t="inlineStr">
         <is>
           <t>GLSS-SM-R080-R1</t>
         </is>
@@ -5674,7 +5662,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="inlineStr">
+      <c r="A188" t="inlineStr">
         <is>
           <t>GLSS-HF-57AE-R1</t>
         </is>
@@ -5702,7 +5690,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="inlineStr">
+      <c r="A189" t="inlineStr">
         <is>
           <t>GLSS-19-0273-TP</t>
         </is>
@@ -5730,7 +5718,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="inlineStr">
+      <c r="A190" t="inlineStr">
         <is>
           <t>GLSS-LU-0B12-TP</t>
         </is>
@@ -5758,7 +5746,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="inlineStr">
+      <c r="A191" t="inlineStr">
         <is>
           <t>GLSS-SM-R102-TP</t>
         </is>
@@ -5786,7 +5774,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="inlineStr">
+      <c r="A192" t="inlineStr">
         <is>
           <t>GLSS-SM-R106-R1</t>
         </is>
@@ -5814,7 +5802,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="inlineStr">
+      <c r="A193" t="inlineStr">
         <is>
           <t>GLSS-SN-0010-R1</t>
         </is>
@@ -5842,7 +5830,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="inlineStr">
+      <c r="A194" t="inlineStr">
         <is>
           <t>GLSS-SM-R068-TP</t>
         </is>
@@ -5870,7 +5858,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="inlineStr">
+      <c r="A195" t="inlineStr">
         <is>
           <t>GLSS-SM-R103-R1</t>
         </is>
@@ -5898,7 +5886,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="inlineStr">
+      <c r="A196" t="inlineStr">
         <is>
           <t>GLSS-SM-R095-R1</t>
         </is>
@@ -5926,7 +5914,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="inlineStr">
+      <c r="A197" t="inlineStr">
         <is>
           <t>GLSS-LX-0304-TP</t>
         </is>
@@ -5954,7 +5942,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="inlineStr">
+      <c r="A198" t="inlineStr">
         <is>
           <t>GLSS-SM-R072-R1</t>
         </is>
@@ -5982,7 +5970,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="inlineStr">
+      <c r="A199" t="inlineStr">
         <is>
           <t>GLSS-HF-3050-R1</t>
         </is>
@@ -6010,7 +5998,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="inlineStr">
+      <c r="A200" t="inlineStr">
         <is>
           <t>GLSS-SN-0004-R1</t>
         </is>
@@ -6038,7 +6026,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="inlineStr">
+      <c r="A201" t="inlineStr">
         <is>
           <t>GLSS-SM-R061-R1</t>
         </is>
@@ -6066,7 +6054,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="inlineStr">
+      <c r="A202" t="inlineStr">
         <is>
           <t>GLSS-SM-R065-R1</t>
         </is>
@@ -6094,7 +6082,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="inlineStr">
+      <c r="A203" t="inlineStr">
         <is>
           <t>GLSS-HF-2934-R1</t>
         </is>
@@ -6122,7 +6110,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="inlineStr">
+      <c r="A204" t="inlineStr">
         <is>
           <t>GLSS-SM-R102-R1</t>
         </is>
@@ -6150,7 +6138,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="inlineStr">
+      <c r="A205" t="inlineStr">
         <is>
           <t>GLSS-SN-0016-R1</t>
         </is>
@@ -6178,7 +6166,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="inlineStr">
+      <c r="A206" t="inlineStr">
         <is>
           <t>GLSS-SM-R104-R1</t>
         </is>
@@ -6206,7 +6194,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="inlineStr">
+      <c r="A207" t="inlineStr">
         <is>
           <t>GLSS-SM-R063-R1</t>
         </is>

--- a/results/qc/glass_expression_QC.xlsx
+++ b/results/qc/glass_expression_QC.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,44 +429,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n_missing</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_negative</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_0</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>n_expressed</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mean_TPM</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>median_TPM</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>max_TPM</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R109-TP</t>
         </is>
@@ -482,7 +494,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0274-TP</t>
         </is>
@@ -510,7 +522,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R005-TP</t>
         </is>
@@ -538,7 +550,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R060-TP</t>
         </is>
@@ -566,7 +578,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>GLSS-LU-00C2-TP</t>
         </is>
@@ -594,7 +606,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>GLSS-LU-00B9-R1</t>
         </is>
@@ -622,7 +634,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>TCGA-06-0210-TP</t>
         </is>
@@ -650,7 +662,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0001-R1</t>
         </is>
@@ -678,7 +690,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>GLSS-MD-0022-TP</t>
         </is>
@@ -706,7 +718,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0267-R1</t>
         </is>
@@ -734,7 +746,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-DF35-TP</t>
         </is>
@@ -762,7 +774,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-6504-TP</t>
         </is>
@@ -790,7 +802,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R107-TP</t>
         </is>
@@ -818,7 +830,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R070-TP</t>
         </is>
@@ -846,7 +858,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R101-R1</t>
         </is>
@@ -874,7 +886,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-P069-TP</t>
         </is>
@@ -902,7 +914,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>TCGA-19-0957-R1</t>
         </is>
@@ -930,7 +942,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0009-TP</t>
         </is>
@@ -958,7 +970,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0271-R1</t>
         </is>
@@ -986,7 +998,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0280-R1</t>
         </is>
@@ -1014,7 +1026,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>GLSS-LX-0304-R1</t>
         </is>
@@ -1042,7 +1054,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R083-TP</t>
         </is>
@@ -1070,7 +1082,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R064-TP</t>
         </is>
@@ -1098,7 +1110,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0002-TP</t>
         </is>
@@ -1126,7 +1138,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R080-TP</t>
         </is>
@@ -1154,7 +1166,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R091-TP</t>
         </is>
@@ -1182,7 +1194,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R106-TP</t>
         </is>
@@ -1210,7 +1222,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0010-TP</t>
         </is>
@@ -1238,7 +1250,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R002-TP</t>
         </is>
@@ -1266,7 +1278,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R091-R1</t>
         </is>
@@ -1294,7 +1306,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-P102-R1</t>
         </is>
@@ -1322,7 +1334,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>TCGA-19-4065-TP</t>
         </is>
@@ -1350,7 +1362,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R082-R1</t>
         </is>
@@ -1378,7 +1390,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0272-R1</t>
         </is>
@@ -1406,7 +1418,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>GLSS-MD-0035-R1</t>
         </is>
@@ -1434,7 +1446,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-9A7A-TP</t>
         </is>
@@ -1462,7 +1474,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-2919-R1</t>
         </is>
@@ -1490,7 +1502,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>GLSS-LU-0B10-TP</t>
         </is>
@@ -1518,7 +1530,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R093-R1</t>
         </is>
@@ -1546,7 +1558,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>TCGA-06-0190-TP</t>
         </is>
@@ -1574,7 +1586,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>TCGA-06-0125-TP</t>
         </is>
@@ -1602,7 +1614,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>GLSS-HK-0001-TP</t>
         </is>
@@ -1630,7 +1642,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-DF35-R1</t>
         </is>
@@ -1658,7 +1670,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R087-TP</t>
         </is>
@@ -1686,7 +1698,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t>GLSS-MD-0026-TP</t>
         </is>
@@ -1714,7 +1726,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R066-TP</t>
         </is>
@@ -1742,7 +1754,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>TCGA-06-0211-R1</t>
         </is>
@@ -1770,7 +1782,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0006-TP</t>
         </is>
@@ -1798,7 +1810,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-6504-R1</t>
         </is>
@@ -1826,7 +1838,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-P003-R1</t>
         </is>
@@ -1854,7 +1866,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R067-TP</t>
         </is>
@@ -1882,7 +1894,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-4D9A-TP</t>
         </is>
@@ -1910,7 +1922,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R081-TP</t>
         </is>
@@ -1938,7 +1950,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R001-R1</t>
         </is>
@@ -1966,7 +1978,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="1" t="inlineStr">
         <is>
           <t>GLSS-LU-00B9-TP</t>
         </is>
@@ -1994,7 +2006,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R061-TP</t>
         </is>
@@ -2022,7 +2034,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="1" t="inlineStr">
         <is>
           <t>GLSS-LU-0B13-R1</t>
         </is>
@@ -2050,7 +2062,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R101-TP</t>
         </is>
@@ -2078,7 +2090,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-9A7A-R1</t>
         </is>
@@ -2106,7 +2118,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R095-TP</t>
         </is>
@@ -2134,7 +2146,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-P069-R1</t>
         </is>
@@ -2162,7 +2174,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-2934-TP</t>
         </is>
@@ -2190,7 +2202,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R107-R1</t>
         </is>
@@ -2218,7 +2230,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="1" t="inlineStr">
         <is>
           <t>GLSS-HK-0003-R1</t>
         </is>
@@ -2246,7 +2258,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R108-R1</t>
         </is>
@@ -2274,7 +2286,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0272-TP</t>
         </is>
@@ -2302,7 +2314,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-P055-TP</t>
         </is>
@@ -2330,7 +2342,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-6658-R1</t>
         </is>
@@ -2358,7 +2370,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R110-R1</t>
         </is>
@@ -2386,7 +2398,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R100-TP</t>
         </is>
@@ -2414,7 +2426,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R007-R1</t>
         </is>
@@ -2442,7 +2454,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0278-TP</t>
         </is>
@@ -2470,7 +2482,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-DE05-R1</t>
         </is>
@@ -2498,7 +2510,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R083-R1</t>
         </is>
@@ -2526,7 +2538,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R068-R1</t>
         </is>
@@ -2554,7 +2566,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R065-TP</t>
         </is>
@@ -2582,7 +2594,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-P055-R1</t>
         </is>
@@ -2610,7 +2622,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="1" t="inlineStr">
         <is>
           <t>TCGA-06-0210-R1</t>
         </is>
@@ -2638,7 +2650,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R112-TP</t>
         </is>
@@ -2666,7 +2678,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R004-R1</t>
         </is>
@@ -2694,7 +2706,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R082-TP</t>
         </is>
@@ -2722,7 +2734,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0009-R1</t>
         </is>
@@ -2750,7 +2762,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-57AE-TP</t>
         </is>
@@ -2778,7 +2790,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="1" t="inlineStr">
         <is>
           <t>GLSS-LU-00C2-R1</t>
         </is>
@@ -2806,7 +2818,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0280-TP</t>
         </is>
@@ -2834,7 +2846,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="1" t="inlineStr">
         <is>
           <t>GLSS-MD-0042-R1</t>
         </is>
@@ -2862,7 +2874,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R003-R1</t>
         </is>
@@ -2890,7 +2902,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-B972-TP</t>
         </is>
@@ -2918,7 +2930,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R003-TP</t>
         </is>
@@ -2946,7 +2958,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="1" t="inlineStr">
         <is>
           <t>GLSS-MD-LP04-R1</t>
         </is>
@@ -2974,7 +2986,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="1" t="inlineStr">
         <is>
           <t>TCGA-06-0211-TP</t>
         </is>
@@ -3002,7 +3014,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="1" t="inlineStr">
         <is>
           <t>GLSS-MD-0035-TP</t>
         </is>
@@ -3030,7 +3042,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-2548-TP</t>
         </is>
@@ -3058,7 +3070,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="1" t="inlineStr">
         <is>
           <t>GLSS-LX-0561-R1</t>
         </is>
@@ -3086,7 +3098,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0273-R1</t>
         </is>
@@ -3114,7 +3126,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-B972-R1</t>
         </is>
@@ -3142,7 +3154,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0004-TP</t>
         </is>
@@ -3170,7 +3182,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="1" t="inlineStr">
         <is>
           <t>TCGA-14-1034-R1</t>
         </is>
@@ -3198,7 +3210,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R060-R1</t>
         </is>
@@ -3226,7 +3238,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-4D9A-R1</t>
         </is>
@@ -3254,7 +3266,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R071-TP</t>
         </is>
@@ -3282,7 +3294,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R006-R1</t>
         </is>
@@ -3310,7 +3322,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0274-R1</t>
         </is>
@@ -3338,7 +3350,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R071-R1</t>
         </is>
@@ -3366,7 +3378,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R081-R1</t>
         </is>
@@ -3394,7 +3406,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-2548-R1</t>
         </is>
@@ -3422,7 +3434,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0016-TP</t>
         </is>
@@ -3450,7 +3462,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R111-R1</t>
         </is>
@@ -3478,7 +3490,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0267-TP</t>
         </is>
@@ -3506,7 +3518,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0002-R1</t>
         </is>
@@ -3534,7 +3546,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0268-TP</t>
         </is>
@@ -3562,7 +3574,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R066-R1</t>
         </is>
@@ -3590,7 +3602,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R109-R1</t>
         </is>
@@ -3618,7 +3630,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="1" t="inlineStr">
         <is>
           <t>GLSS-LU-00C1-R1</t>
         </is>
@@ -3646,7 +3658,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="1" t="inlineStr">
         <is>
           <t>GLSS-MD-LP04-TP</t>
         </is>
@@ -3674,7 +3686,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-2919-TP</t>
         </is>
@@ -3702,7 +3714,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R019-R1</t>
         </is>
@@ -3730,7 +3742,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-1DDC-R1</t>
         </is>
@@ -3758,7 +3770,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-6658-TP</t>
         </is>
@@ -3786,7 +3798,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0268-R1</t>
         </is>
@@ -3814,7 +3826,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R099-R1</t>
         </is>
@@ -3842,7 +3854,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R006-TP</t>
         </is>
@@ -3870,7 +3882,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0269-R1</t>
         </is>
@@ -3898,7 +3910,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R104-TP</t>
         </is>
@@ -3926,7 +3938,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0269-TP</t>
         </is>
@@ -3954,7 +3966,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-EE74-TP</t>
         </is>
@@ -3982,7 +3994,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-3050-TP</t>
         </is>
@@ -4010,7 +4022,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R064-R1</t>
         </is>
@@ -4038,7 +4050,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="1" t="inlineStr">
         <is>
           <t>GLSS-MD-0042-TP</t>
         </is>
@@ -4066,7 +4078,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-1DDC-TP</t>
         </is>
@@ -4094,7 +4106,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R008-TP</t>
         </is>
@@ -4122,7 +4134,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R103-TP</t>
         </is>
@@ -4150,7 +4162,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="1" t="inlineStr">
         <is>
           <t>GLSS-LX-0561-TP</t>
         </is>
@@ -4178,7 +4190,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-DE05-TP</t>
         </is>
@@ -4206,7 +4218,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="1" t="inlineStr">
         <is>
           <t>TCGA-06-0190-R1</t>
         </is>
@@ -4234,7 +4246,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R085-R1</t>
         </is>
@@ -4262,7 +4274,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="1" t="inlineStr">
         <is>
           <t>GLSS-LU-0B10-R1</t>
         </is>
@@ -4290,7 +4302,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0006-R1</t>
         </is>
@@ -4318,7 +4330,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="1" t="inlineStr">
         <is>
           <t>GLSS-MD-0022-R1</t>
         </is>
@@ -4346,7 +4358,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R087-R1</t>
         </is>
@@ -4374,7 +4386,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R112-R1</t>
         </is>
@@ -4402,7 +4414,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-3162-TP</t>
         </is>
@@ -4430,7 +4442,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R072-TP</t>
         </is>
@@ -4458,7 +4470,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R108-TP</t>
         </is>
@@ -4486,7 +4498,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="1" t="inlineStr">
         <is>
           <t>TCGA-19-0957-TP</t>
         </is>
@@ -4514,7 +4526,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R099-TP</t>
         </is>
@@ -4542,7 +4554,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="A148" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R010-TP</t>
         </is>
@@ -4570,7 +4582,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0001-TP</t>
         </is>
@@ -4598,7 +4610,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0278-R1</t>
         </is>
@@ -4626,7 +4638,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R005-R1</t>
         </is>
@@ -4654,7 +4666,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0003-TP</t>
         </is>
@@ -4682,7 +4694,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R063-TP</t>
         </is>
@@ -4710,7 +4722,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R004-TP</t>
         </is>
@@ -4738,7 +4750,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="1" t="inlineStr">
         <is>
           <t>TCGA-19-4065-R1</t>
         </is>
@@ -4766,7 +4778,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R093-TP</t>
         </is>
@@ -4794,7 +4806,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R110-TP</t>
         </is>
@@ -4822,7 +4834,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0003-R1</t>
         </is>
@@ -4850,7 +4862,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-P046-TP</t>
         </is>
@@ -4878,7 +4890,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="1" t="inlineStr">
         <is>
           <t>GLSS-LU-0B13-TP</t>
         </is>
@@ -4906,7 +4918,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="A161" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R088-TP</t>
         </is>
@@ -4934,7 +4946,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R001-TP</t>
         </is>
@@ -4962,7 +4974,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R019-TP</t>
         </is>
@@ -4990,7 +5002,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
+      <c r="A164" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-3162-R1</t>
         </is>
@@ -5018,7 +5030,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
+      <c r="A165" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0271-TP</t>
         </is>
@@ -5046,7 +5058,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
+      <c r="A166" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R085-TP</t>
         </is>
@@ -5074,7 +5086,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
+      <c r="A167" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R010-R1</t>
         </is>
@@ -5102,7 +5114,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
+      <c r="A168" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-P102-TP</t>
         </is>
@@ -5130,7 +5142,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
+      <c r="A169" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R008-R1</t>
         </is>
@@ -5158,7 +5170,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
+      <c r="A170" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R088-R1</t>
         </is>
@@ -5186,7 +5198,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="1" t="inlineStr">
         <is>
           <t>TCGA-06-0125-R1</t>
         </is>
@@ -5214,7 +5226,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="1" t="inlineStr">
         <is>
           <t>GLSS-HK-0001-R1</t>
         </is>
@@ -5242,7 +5254,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
+      <c r="A173" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R007-TP</t>
         </is>
@@ -5270,7 +5282,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="A174" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R070-R1</t>
         </is>
@@ -5298,7 +5310,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="A175" s="1" t="inlineStr">
         <is>
           <t>GLSS-LU-0B12-R1</t>
         </is>
@@ -5326,7 +5338,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="1" t="inlineStr">
         <is>
           <t>TCGA-14-1034-TP</t>
         </is>
@@ -5354,7 +5366,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-P003-TP</t>
         </is>
@@ -5382,7 +5394,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="A178" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-P046-R1</t>
         </is>
@@ -5410,7 +5422,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
+      <c r="A179" s="1" t="inlineStr">
         <is>
           <t>GLSS-LU-00C1-TP</t>
         </is>
@@ -5438,7 +5450,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
+      <c r="A180" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R111-TP</t>
         </is>
@@ -5466,7 +5478,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
+      <c r="A181" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R067-R1</t>
         </is>
@@ -5494,7 +5506,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
+      <c r="A182" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R100-R1</t>
         </is>
@@ -5522,7 +5534,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
+      <c r="A183" s="1" t="inlineStr">
         <is>
           <t>GLSS-MD-0026-R1</t>
         </is>
@@ -5550,7 +5562,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
+      <c r="A184" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-EE74-R1</t>
         </is>
@@ -5578,7 +5590,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
+      <c r="A185" s="1" t="inlineStr">
         <is>
           <t>GLSS-CU-R002-R1</t>
         </is>
@@ -5606,7 +5618,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="1" t="inlineStr">
         <is>
           <t>GLSS-HK-0003-TP</t>
         </is>
@@ -5634,7 +5646,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R080-R1</t>
         </is>
@@ -5662,7 +5674,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
+      <c r="A188" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-57AE-R1</t>
         </is>
@@ -5690,7 +5702,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
+      <c r="A189" s="1" t="inlineStr">
         <is>
           <t>GLSS-19-0273-TP</t>
         </is>
@@ -5718,7 +5730,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
+      <c r="A190" s="1" t="inlineStr">
         <is>
           <t>GLSS-LU-0B12-TP</t>
         </is>
@@ -5746,7 +5758,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
+      <c r="A191" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R102-TP</t>
         </is>
@@ -5774,7 +5786,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
+      <c r="A192" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R106-R1</t>
         </is>
@@ -5802,7 +5814,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
+      <c r="A193" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0010-R1</t>
         </is>
@@ -5830,7 +5842,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R068-TP</t>
         </is>
@@ -5858,7 +5870,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
+      <c r="A195" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R103-R1</t>
         </is>
@@ -5886,7 +5898,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
+      <c r="A196" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R095-R1</t>
         </is>
@@ -5914,7 +5926,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
+      <c r="A197" s="1" t="inlineStr">
         <is>
           <t>GLSS-LX-0304-TP</t>
         </is>
@@ -5942,7 +5954,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
+      <c r="A198" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R072-R1</t>
         </is>
@@ -5970,7 +5982,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
+      <c r="A199" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-3050-R1</t>
         </is>
@@ -5998,7 +6010,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
+      <c r="A200" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0004-R1</t>
         </is>
@@ -6026,7 +6038,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="A201" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R061-R1</t>
         </is>
@@ -6054,7 +6066,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
+      <c r="A202" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R065-R1</t>
         </is>
@@ -6082,7 +6094,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
+      <c r="A203" s="1" t="inlineStr">
         <is>
           <t>GLSS-HF-2934-R1</t>
         </is>
@@ -6110,7 +6122,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
+      <c r="A204" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R102-R1</t>
         </is>
@@ -6138,7 +6150,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
+      <c r="A205" s="1" t="inlineStr">
         <is>
           <t>GLSS-SN-0016-R1</t>
         </is>
@@ -6166,7 +6178,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
+      <c r="A206" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R104-R1</t>
         </is>
@@ -6194,7 +6206,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
+      <c r="A207" s="1" t="inlineStr">
         <is>
           <t>GLSS-SM-R063-R1</t>
         </is>
